--- a/report_forms/033_storage_humidity_control_report_form--report_forms.xlsx
+++ b/report_forms/033_storage_humidity_control_report_form--report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>storage-location</t>
+          <t>What is the storage location for this report?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,13 +548,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>start-date</t>
+          <t>When was the start date for this storage?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,13 +571,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>corrective-actions</t>
+          <t>What corrective actions were taken?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -594,13 +594,13 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>environmental-monitoring</t>
+          <t>How often is environmental monitoring conducted?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -617,36 +617,36 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>temperature-checks</t>
+          <t>What temperature checks were conducted?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>corrective_actions</t>
+          <t>storage_humidity_controls</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>corrective-actions</t>
+          <t>What storage humidity controls are in place?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>storage_location</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>storage-location</t>
+          <t>Are there any notes to report?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>temperature_checks</t>
+          <t>environmental_monitoring_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>temperature-checks</t>
+          <t>How often is environmental monitoring conducted (again)?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>environmental_monitoring</t>
+          <t>temperature_checks_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>environmental-monitoring</t>
+          <t>What temperature checks were conducted (again)?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>corrective_actions_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>What corrective actions were taken (again)?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,62 +750,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>storage_humidity_controls</t>
+          <t>storage_humidity_controls_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>storage-humidity-controls</t>
+          <t>What are the storage humidity controls in place (again)?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>corrective_actions</t>
+          <t>other_comments</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>corrective-actions</t>
+          <t>Are there any other comments or notes?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>environmental_monitoring_2</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>environmental-monitoring-2</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -822,7 +799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1003,58 +980,58 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>corrective_actions_choices</t>
+          <t>environmental_monitoring_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>corrective-action-1</t>
+          <t>environmental-monitoring-2-1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>corrective-action-1</t>
+          <t>environmental-monitoring-2-1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>corrective_actions_choices</t>
+          <t>environmental_monitoring_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>corrective-action-2</t>
+          <t>environmental-monitoring-2-2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>corrective-action-2</t>
+          <t>environmental-monitoring-2-2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>corrective_actions_choices</t>
+          <t>environmental_monitoring_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>corrective-action-3</t>
+          <t>environmental-monitoring-2-3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>corrective-action-3</t>
+          <t>environmental-monitoring-2-3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>temperature_checks_choices</t>
+          <t>temperature_checks_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1071,7 +1048,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>temperature_checks_choices</t>
+          <t>temperature_checks_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1088,7 +1065,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>temperature_checks_choices</t>
+          <t>temperature_checks_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1105,153 +1082,51 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>environmental_monitoring_choices</t>
+          <t>corrective_actions_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>environmental-monitoring-1</t>
+          <t>corrective-action-1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>environmental-monitoring-1</t>
+          <t>corrective-action-1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>environmental_monitoring_choices</t>
+          <t>corrective_actions_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>environmental-monitoring-2</t>
+          <t>corrective-action-2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>environmental-monitoring-2</t>
+          <t>corrective-action-2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>environmental_monitoring_choices</t>
+          <t>corrective_actions_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>environmental-monitoring-3</t>
+          <t>corrective-action-3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>environmental-monitoring-3</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>corrective_actions_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>corrective-action-1</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>corrective-action-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>corrective_actions_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>corrective-action-2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>corrective-action-2</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>corrective_actions_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
           <t>corrective-action-3</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>corrective-action-3</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>environmental_monitoring_2_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>environmental-monitoring-2-1</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>environmental-monitoring-2-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>environmental_monitoring_2_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>environmental-monitoring-2-2</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>environmental-monitoring-2-2</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>environmental_monitoring_2_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>environmental-monitoring-2-3</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>environmental-monitoring-2-3</t>
         </is>
       </c>
     </row>
